--- a/data/trans_orig/LAWTONB_2R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24692</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43186</t>
+          <t>43876</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>38,16%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>34645</t>
+          <t>35338</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>57357</t>
+          <t>58682</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,63%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>39,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>66465</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>95543</t>
+          <t>96089</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,12%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71803</t>
+          <t>71113</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>90297</t>
+          <t>89576</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,44%</t>
+          <t>61,84%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92178</t>
+          <t>90853</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114890</t>
+          <t>114197</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>60,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,37%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168981</t>
+          <t>168435</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>198059</t>
+          <t>199583</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,67%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>74,87%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36437</t>
+          <t>37141</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58545</t>
+          <t>59755</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,98%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,13%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55900</t>
+          <t>55575</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>82914</t>
+          <t>83734</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,6%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>45,84%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100223</t>
+          <t>99694</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>134786</t>
+          <t>133648</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,5%</t>
+          <t>30,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,02%</t>
+          <t>40,68%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87344</t>
+          <t>86134</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>109452</t>
+          <t>108748</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,87%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,02%</t>
+          <t>74,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>99766</t>
+          <t>98946</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>126780</t>
+          <t>127105</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,4%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>193782</t>
+          <t>194920</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228345</t>
+          <t>228874</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>58,98%</t>
+          <t>59,32%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,66%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14417</t>
+          <t>13604</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31754</t>
+          <t>30794</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,03%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36106</t>
+          <t>36277</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58403</t>
+          <t>57224</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>42,12%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>52069</t>
+          <t>54535</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>81887</t>
+          <t>83205</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,09%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>72617</t>
+          <t>73577</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>89954</t>
+          <t>90767</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>70,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,97%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>77447</t>
+          <t>78626</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99744</t>
+          <t>99573</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,01%</t>
+          <t>57,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>73,3%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>158334</t>
+          <t>157016</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>188152</t>
+          <t>185686</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,91%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,32%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20579</t>
+          <t>20992</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37576</t>
+          <t>38371</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59062</t>
+          <t>58555</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>86094</t>
+          <t>85338</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,24%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>84479</t>
+          <t>85250</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118162</t>
+          <t>118466</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,24%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>99641</t>
+          <t>98846</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116638</t>
+          <t>116225</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>122683</t>
+          <t>123439</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>149715</t>
+          <t>150222</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>59,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,71%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227833</t>
+          <t>227529</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>261516</t>
+          <t>260745</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,58%</t>
+          <t>75,36%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>114697</t>
+          <t>115143</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>151761</t>
+          <t>152959</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,2%</t>
+          <t>30,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>207894</t>
+          <t>209951</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>257407</t>
+          <t>260274</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>30,72%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>330432</t>
+          <t>332744</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>395194</t>
+          <t>395723</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>33,56%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>350705</t>
+          <t>349507</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387769</t>
+          <t>387323</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,8%</t>
+          <t>69,56%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,08%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>419435</t>
+          <t>416568</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>468948</t>
+          <t>466891</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,97%</t>
+          <t>61,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,28%</t>
+          <t>68,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>784114</t>
+          <t>783585</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>848876</t>
+          <t>846564</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,49%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,78%</t>
         </is>
       </c>
     </row>
@@ -2485,7 +2485,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25323</t>
+          <t>24709</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45985</t>
+          <t>45032</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>32,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50199</t>
+          <t>50439</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>75446</t>
+          <t>74511</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2730,12 +2730,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,24%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>45,23%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80117</t>
+          <t>80945</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>113781</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,25%</t>
+          <t>37,14%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93562</t>
+          <t>94515</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114224</t>
+          <t>114838</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,85%</t>
+          <t>82,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>91341</t>
+          <t>92276</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116588</t>
+          <t>116348</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,12 +2843,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>54,77%</t>
+          <t>55,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,76%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192234</t>
+          <t>192553</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>226217</t>
+          <t>225389</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,75%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,58%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>34604</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58440</t>
+          <t>58619</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>22,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,73%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75757</t>
+          <t>74090</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102346</t>
+          <t>104047</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>39,58%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>54,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116448</t>
+          <t>117496</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>153370</t>
+          <t>155024</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,63%</t>
+          <t>33,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,29%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96438</t>
+          <t>96259</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>121848</t>
+          <t>120274</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,27%</t>
+          <t>62,15%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>77,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>89074</t>
+          <t>87373</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>115663</t>
+          <t>117330</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>45,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>60,42%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>192928</t>
+          <t>191274</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>229850</t>
+          <t>228802</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,71%</t>
+          <t>55,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,37%</t>
+          <t>66,07%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17770</t>
+          <t>18543</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>39187</t>
+          <t>38556</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,83%</t>
+          <t>37,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41399</t>
+          <t>41779</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64473</t>
+          <t>65511</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>45,72%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>66466</t>
+          <t>65120</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97748</t>
+          <t>97154</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>26,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>39,72%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64411</t>
+          <t>65042</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85828</t>
+          <t>85055</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,17%</t>
+          <t>62,78%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76546</t>
+          <t>75508</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99620</t>
+          <t>99240</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>53,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>146869</t>
+          <t>147463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>178151</t>
+          <t>179497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>60,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,83%</t>
+          <t>73,38%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>31472</t>
+          <t>30426</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>55519</t>
+          <t>54845</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>18,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67494</t>
+          <t>67393</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>98063</t>
+          <t>97906</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>107295</t>
+          <t>105849</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>146036</t>
+          <t>143336</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>36,03%</t>
+          <t>35,36%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106094</t>
+          <t>106768</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>130141</t>
+          <t>131187</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,65%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>80,53%</t>
+          <t>81,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145687</t>
+          <t>145844</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176256</t>
+          <t>176357</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>259327</t>
+          <t>262027</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>298068</t>
+          <t>299514</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>63,97%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>73,89%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>129139</t>
+          <t>127667</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>173471</t>
+          <t>172407</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>31,0%</t>
+          <t>30,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>261377</t>
+          <t>260717</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>315014</t>
+          <t>316377</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,18%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400951</t>
+          <t>400732</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>471055</t>
+          <t>470735</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,78%</t>
+          <t>30,76%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,16%</t>
+          <t>36,14%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386166</t>
+          <t>387230</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>430498</t>
+          <t>431970</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,0%</t>
+          <t>69,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>77,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>427961</t>
+          <t>426598</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>481598</t>
+          <t>482258</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>64,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>831557</t>
+          <t>831877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>901661</t>
+          <t>901880</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,84%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,22%</t>
+          <t>69,24%</t>
         </is>
       </c>
     </row>
@@ -4432,7 +4432,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19637</t>
+          <t>19575</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37528</t>
+          <t>36702</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,45%</t>
+          <t>26,84%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>48372</t>
+          <t>47471</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74897</t>
+          <t>73513</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,9%</t>
+          <t>27,38%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,2%</t>
+          <t>42,4%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>72654</t>
+          <t>73530</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104805</t>
+          <t>104536</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,43%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>33,71%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99206</t>
+          <t>100032</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117097</t>
+          <t>117159</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,55%</t>
+          <t>73,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,64%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>98494</t>
+          <t>99878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125019</t>
+          <t>125920</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,1%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205320</t>
+          <t>205589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>237471</t>
+          <t>236595</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,21%</t>
+          <t>66,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,57%</t>
+          <t>76,29%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30881</t>
+          <t>30253</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51366</t>
+          <t>51628</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,72%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,14%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>65020</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>96664</t>
+          <t>98064</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>30,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,11%</t>
+          <t>44,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>100627</t>
+          <t>102772</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>138662</t>
+          <t>142183</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,1%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113575</t>
+          <t>113313</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134060</t>
+          <t>134688</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,86%</t>
+          <t>68,7%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,28%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>122499</t>
+          <t>121099</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>154143</t>
+          <t>153158</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,33%</t>
+          <t>69,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>245442</t>
+          <t>241921</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>283477</t>
+          <t>281332</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,9%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,24%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18191</t>
+          <t>18155</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35134</t>
+          <t>36036</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>30,54%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42853</t>
+          <t>42675</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>66418</t>
+          <t>68105</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,93%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,58%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65612</t>
+          <t>64941</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96448</t>
+          <t>96523</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,47%</t>
+          <t>25,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,47%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>79901</t>
+          <t>78999</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96844</t>
+          <t>96880</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,46%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,22%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>76178</t>
+          <t>74491</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99743</t>
+          <t>99921</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,42%</t>
+          <t>52,24%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161183</t>
+          <t>161108</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192019</t>
+          <t>192690</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,53%</t>
+          <t>74,79%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20838</t>
+          <t>21099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>39092</t>
+          <t>40298</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>22,39%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67479</t>
+          <t>67149</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102237</t>
+          <t>100876</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,79%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>41,55%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>95046</t>
+          <t>94920</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133612</t>
+          <t>133584</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>32,0%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>135526</t>
+          <t>134320</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153780</t>
+          <t>153519</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>77,61%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>140544</t>
+          <t>141905</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175302</t>
+          <t>175632</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283788</t>
+          <t>283816</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322354</t>
+          <t>322480</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,23%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>106103</t>
+          <t>105641</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>142797</t>
+          <t>143942</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>247689</t>
+          <t>251097</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>304264</t>
+          <t>306449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,11%</t>
+          <t>39,39%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>370897</t>
+          <t>367801</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>440086</t>
+          <t>438824</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>26,86%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,05%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>448531</t>
+          <t>447386</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485225</t>
+          <t>485687</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,66%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,06%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>473667</t>
+          <t>471482</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>530242</t>
+          <t>526834</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>67,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>929173</t>
+          <t>930435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>998362</t>
+          <t>1001458</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>73,14%</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023</t>
+          <t>Población con algún grado de dependencia funcional para actividades instrumentales de la vida diaria (Lawton y Brody) en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6574,12 +6574,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41446</t>
+          <t>41749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>59597</t>
+          <t>60580</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6589,12 +6589,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,99%</t>
+          <t>28,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,25%</t>
+          <t>40,91%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6609,12 +6609,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74962</t>
+          <t>74982</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>91854</t>
+          <t>90985</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6624,12 +6624,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,08%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,56%</t>
+          <t>51,08%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6644,12 +6644,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>122434</t>
+          <t>121879</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>147028</t>
+          <t>146680</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6659,12 +6659,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,53%</t>
+          <t>37,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>44,96%</t>
         </is>
       </c>
     </row>
@@ -6687,12 +6687,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>88486</t>
+          <t>87503</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106637</t>
+          <t>106334</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6702,12 +6702,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,09%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,01%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6722,12 +6722,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>86279</t>
+          <t>87148</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103171</t>
+          <t>103151</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6737,12 +6737,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,44%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,92%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6757,12 +6757,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179188</t>
+          <t>179536</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>203782</t>
+          <t>204337</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6772,12 +6772,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>55,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,64%</t>
         </is>
       </c>
     </row>
@@ -6917,12 +6917,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32654</t>
+          <t>34368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50438</t>
+          <t>51193</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6932,12 +6932,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,39%</t>
+          <t>21,46%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,5%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6952,12 +6952,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81582</t>
+          <t>80767</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101488</t>
+          <t>101266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -6967,12 +6967,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,66%</t>
+          <t>46,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119728</t>
+          <t>119042</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147763</t>
+          <t>147180</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7002,12 +7002,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>39,13%</t>
+          <t>38,97%</t>
         </is>
       </c>
     </row>
@@ -7030,12 +7030,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>109676</t>
+          <t>108921</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>127460</t>
+          <t>125746</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7045,12 +7045,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,5%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>78,54%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7065,12 +7065,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116037</t>
+          <t>116259</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>135943</t>
+          <t>136758</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7080,12 +7080,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,34%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7100,12 +7100,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>229877</t>
+          <t>230460</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>257912</t>
+          <t>258598</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7115,12 +7115,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>60,87%</t>
+          <t>61,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -7260,12 +7260,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20172</t>
+          <t>20096</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36062</t>
+          <t>36544</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7275,12 +7275,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7295,12 +7295,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16723</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>145799</t>
+          <t>149080</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7315,7 +7315,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>41,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7330,12 +7330,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>32719</t>
+          <t>36968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>155972</t>
+          <t>157919</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7345,12 +7345,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,49%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -7373,12 +7373,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>99397</t>
+          <t>98915</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115287</t>
+          <t>115363</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7388,12 +7388,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,16%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7408,12 +7408,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>214004</t>
+          <t>210723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343089</t>
+          <t>343080</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -7443,12 +7443,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>339291</t>
+          <t>337344</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>462544</t>
+          <t>458295</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7458,12 +7458,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,51%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>93,39%</t>
+          <t>92,54%</t>
         </is>
       </c>
     </row>
@@ -7603,12 +7603,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34521</t>
+          <t>34763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52254</t>
+          <t>52202</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,03%</t>
+          <t>26,0%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7638,12 +7638,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>93526</t>
+          <t>94249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>117831</t>
+          <t>118477</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7653,12 +7653,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,04%</t>
+          <t>43,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7673,12 +7673,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>134466</t>
+          <t>133344</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>165501</t>
+          <t>163935</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7688,12 +7688,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,34%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>34,55%</t>
         </is>
       </c>
     </row>
@@ -7716,12 +7716,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148494</t>
+          <t>148546</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>166227</t>
+          <t>165985</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7731,12 +7731,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>74,0%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,8%</t>
+          <t>82,68%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7751,12 +7751,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155931</t>
+          <t>155285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>180236</t>
+          <t>179513</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,96%</t>
+          <t>56,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,57%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7786,12 +7786,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>309009</t>
+          <t>310575</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>340044</t>
+          <t>341166</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7801,12 +7801,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,66%</t>
+          <t>71,9%</t>
         </is>
       </c>
     </row>
@@ -7946,12 +7946,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145980</t>
+          <t>145589</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>181314</t>
+          <t>180902</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7961,12 +7961,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>22,59%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,07%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>178478</t>
+          <t>179236</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>434506</t>
+          <t>433745</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7996,12 +7996,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,22%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8016,12 +8016,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>352520</t>
+          <t>344724</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>584126</t>
+          <t>586783</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>34,9%</t>
+          <t>35,06%</t>
         </is>
       </c>
     </row>
@@ -8059,12 +8059,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463090</t>
+          <t>463502</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498424</t>
+          <t>498815</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8074,12 +8074,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>77,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8094,12 +8094,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>594718</t>
+          <t>595479</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>850746</t>
+          <t>849988</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8109,12 +8109,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8129,12 +8129,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1089502</t>
+          <t>1086845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1321108</t>
+          <t>1328904</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>65,1%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,4%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/LAWTONB_2R2-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/LAWTONB_2R2-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>24925</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>43876</t>
+          <t>43757</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>22,1%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,16%</t>
+          <t>38,05%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35338</t>
+          <t>35063</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58682</t>
+          <t>57348</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>39,24%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>64941</t>
+          <t>65638</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>96089</t>
+          <t>96202</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,37%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>71113</t>
+          <t>71232</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>89576</t>
+          <t>90064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,84%</t>
+          <t>61,95%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>77,9%</t>
+          <t>78,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>90853</t>
+          <t>92187</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>114197</t>
+          <t>114472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>60,76%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>76,37%</t>
+          <t>76,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>168435</t>
+          <t>168322</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>199583</t>
+          <t>198886</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,45%</t>
+          <t>75,19%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37141</t>
+          <t>37644</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59755</t>
+          <t>60003</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>25,46%</t>
+          <t>25,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>41,13%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>55575</t>
+          <t>55446</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>83734</t>
+          <t>81982</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,35%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>99694</t>
+          <t>99878</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133648</t>
+          <t>135662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,68%</t>
+          <t>41,29%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86134</t>
+          <t>85886</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108748</t>
+          <t>108245</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,04%</t>
+          <t>58,87%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>74,54%</t>
+          <t>74,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>98946</t>
+          <t>100698</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>127105</t>
+          <t>127234</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>194920</t>
+          <t>192906</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228874</t>
+          <t>228690</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>58,71%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,6%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13604</t>
+          <t>13889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>30794</t>
+          <t>30429</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>13,03%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,5%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>36277</t>
+          <t>36194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57224</t>
+          <t>57922</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>26,7%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,12%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>54535</t>
+          <t>53800</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>83205</t>
+          <t>82350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,64%</t>
+          <t>34,28%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>73577</t>
+          <t>73942</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>90767</t>
+          <t>90482</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,5%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>86,97%</t>
+          <t>86,69%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>78626</t>
+          <t>77928</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99573</t>
+          <t>99656</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,88%</t>
+          <t>57,36%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>73,3%</t>
+          <t>73,36%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>157016</t>
+          <t>157871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185686</t>
+          <t>186421</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,36%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,6%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>19598</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>38371</t>
+          <t>38406</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,3%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,96%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58555</t>
+          <t>57920</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>85338</t>
+          <t>85470</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,88%</t>
+          <t>40,94%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>85250</t>
+          <t>83986</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>118466</t>
+          <t>116717</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,64%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,73%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>98846</t>
+          <t>98811</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>116225</t>
+          <t>117619</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,04%</t>
+          <t>72,01%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,7%</t>
+          <t>85,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>123439</t>
+          <t>123307</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>150222</t>
+          <t>150857</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,12%</t>
+          <t>59,06%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>227529</t>
+          <t>229278</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>260745</t>
+          <t>262009</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,73%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>115143</t>
+          <t>114256</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152959</t>
+          <t>153418</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,44%</t>
+          <t>30,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>209951</t>
+          <t>209277</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>260274</t>
+          <t>259970</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>332744</t>
+          <t>334693</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>395723</t>
+          <t>394645</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,22%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>33,46%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>349507</t>
+          <t>349048</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>387323</t>
+          <t>388210</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,56%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,08%</t>
+          <t>77,26%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>416568</t>
+          <t>416872</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>466891</t>
+          <t>467565</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>68,98%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>784663</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>846564</t>
+          <t>844615</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>66,54%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,62%</t>
         </is>
       </c>
     </row>
@@ -2680,12 +2680,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24709</t>
+          <t>24359</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>45032</t>
+          <t>45662</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2695,12 +2695,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>32,27%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2715,12 +2715,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50439</t>
+          <t>50430</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74511</t>
+          <t>74756</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>44,67%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2750,12 +2750,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>80945</t>
+          <t>80241</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>113781</t>
+          <t>113651</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2765,12 +2765,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>37,1%</t>
         </is>
       </c>
     </row>
@@ -2793,12 +2793,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>94515</t>
+          <t>93885</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>114838</t>
+          <t>115188</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2808,12 +2808,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>67,73%</t>
+          <t>67,28%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>92276</t>
+          <t>92031</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116348</t>
+          <t>116357</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>55,33%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>192553</t>
+          <t>192683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>225389</t>
+          <t>226093</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2878,12 +2878,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,9%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>73,58%</t>
+          <t>73,81%</t>
         </is>
       </c>
     </row>
@@ -3023,12 +3023,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34604</t>
+          <t>34435</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>58619</t>
+          <t>57587</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3038,12 +3038,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,85%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -3058,12 +3058,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74090</t>
+          <t>76289</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>104047</t>
+          <t>102934</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3073,12 +3073,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>39,85%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>54,36%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -3093,12 +3093,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>117496</t>
+          <t>116908</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>155024</t>
+          <t>153795</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -3108,12 +3108,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>33,93%</t>
+          <t>33,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,41%</t>
         </is>
       </c>
     </row>
@@ -3136,12 +3136,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96259</t>
+          <t>97291</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>120274</t>
+          <t>120443</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3151,12 +3151,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>62,15%</t>
+          <t>62,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,66%</t>
+          <t>77,77%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3171,12 +3171,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>87373</t>
+          <t>88486</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>117330</t>
+          <t>115131</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3186,12 +3186,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,64%</t>
+          <t>46,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>191274</t>
+          <t>192503</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>228802</t>
+          <t>229390</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3221,12 +3221,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>55,23%</t>
+          <t>55,59%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>66,07%</t>
+          <t>66,24%</t>
         </is>
       </c>
     </row>
@@ -3366,12 +3366,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18543</t>
+          <t>18627</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>38556</t>
+          <t>39056</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3381,12 +3381,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3401,12 +3401,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>41779</t>
+          <t>40296</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>65511</t>
+          <t>65126</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3416,12 +3416,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>28,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3436,12 +3436,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>65120</t>
+          <t>65199</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>97154</t>
+          <t>95266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>26,62%</t>
+          <t>26,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>39,72%</t>
+          <t>38,94%</t>
         </is>
       </c>
     </row>
@@ -3479,12 +3479,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>65042</t>
+          <t>64542</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>85055</t>
+          <t>84971</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3494,12 +3494,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>82,02%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3514,12 +3514,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75508</t>
+          <t>75893</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99240</t>
+          <t>100723</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3529,12 +3529,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,37%</t>
+          <t>71,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3549,12 +3549,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>147463</t>
+          <t>149351</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>179497</t>
+          <t>179418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3564,12 +3564,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>61,06%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>73,38%</t>
+          <t>73,35%</t>
         </is>
       </c>
     </row>
@@ -3709,12 +3709,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>30426</t>
+          <t>31607</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>54845</t>
+          <t>55171</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3724,12 +3724,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,83%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>34,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3744,12 +3744,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67393</t>
+          <t>67410</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>97906</t>
+          <t>97516</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3759,12 +3759,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,66%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>40,17%</t>
+          <t>40,01%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3779,12 +3779,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>105849</t>
+          <t>106022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143336</t>
+          <t>143724</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3794,12 +3794,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>35,36%</t>
+          <t>35,46%</t>
         </is>
       </c>
     </row>
@@ -3822,12 +3822,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>106768</t>
+          <t>106442</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>131187</t>
+          <t>130006</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>66,06%</t>
+          <t>65,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,17%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3857,12 +3857,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>145844</t>
+          <t>146234</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>176357</t>
+          <t>176340</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3872,12 +3872,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>59,83%</t>
+          <t>59,99%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3892,12 +3892,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>262027</t>
+          <t>261639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>299514</t>
+          <t>299341</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3907,12 +3907,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>64,54%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,89%</t>
+          <t>73,85%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>127667</t>
+          <t>127896</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>172407</t>
+          <t>172620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,81%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>260717</t>
+          <t>258686</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>316377</t>
+          <t>313752</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>35,09%</t>
+          <t>34,82%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,58%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>400732</t>
+          <t>400904</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>470735</t>
+          <t>469767</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>30,78%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,14%</t>
+          <t>36,06%</t>
         </is>
       </c>
     </row>
@@ -4165,12 +4165,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>387230</t>
+          <t>387017</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>431970</t>
+          <t>431741</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4180,12 +4180,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,19%</t>
+          <t>77,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4200,12 +4200,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>426598</t>
+          <t>429223</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>482258</t>
+          <t>484289</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4215,12 +4215,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,42%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>64,91%</t>
+          <t>65,18%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4235,12 +4235,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>831877</t>
+          <t>832845</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>901880</t>
+          <t>901708</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4250,12 +4250,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>63,86%</t>
+          <t>63,94%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>69,24%</t>
+          <t>69,22%</t>
         </is>
       </c>
     </row>
@@ -4627,12 +4627,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19575</t>
+          <t>18901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36702</t>
+          <t>36822</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4642,12 +4642,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,93%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4662,12 +4662,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>47471</t>
+          <t>46922</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>73513</t>
+          <t>73449</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4677,12 +4677,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>27,38%</t>
+          <t>27,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,4%</t>
+          <t>42,36%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4697,12 +4697,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>73530</t>
+          <t>72033</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>104536</t>
+          <t>105442</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4712,12 +4712,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100032</t>
+          <t>99912</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>117159</t>
+          <t>117833</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,16%</t>
+          <t>73,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,68%</t>
+          <t>86,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>99878</t>
+          <t>99942</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>125920</t>
+          <t>126469</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,6%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>72,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>205589</t>
+          <t>204683</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>236595</t>
+          <t>238092</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,29%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>76,29%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -4970,12 +4970,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>30253</t>
+          <t>31861</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51628</t>
+          <t>51669</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4985,12 +4985,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,34%</t>
+          <t>19,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5005,12 +5005,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66005</t>
+          <t>65197</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>98064</t>
+          <t>95949</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5020,12 +5020,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,74%</t>
+          <t>43,78%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5040,12 +5040,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>102772</t>
+          <t>101921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>142183</t>
+          <t>141297</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5055,12 +5055,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,79%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>113313</t>
+          <t>113272</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>134688</t>
+          <t>133080</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,7%</t>
+          <t>68,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,66%</t>
+          <t>80,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>121099</t>
+          <t>123214</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>153158</t>
+          <t>153966</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>55,26%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>70,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>241921</t>
+          <t>242807</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>281332</t>
+          <t>282183</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,21%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,24%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -5313,12 +5313,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18155</t>
+          <t>18255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36036</t>
+          <t>35889</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>31,33%</t>
+          <t>31,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>42675</t>
+          <t>42010</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68105</t>
+          <t>66971</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>29,93%</t>
+          <t>29,46%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5383,12 +5383,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>64941</t>
+          <t>65403</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>96523</t>
+          <t>97168</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,21%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>78999</t>
+          <t>79146</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>96880</t>
+          <t>96780</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>68,67%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>84,22%</t>
+          <t>84,13%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74491</t>
+          <t>75625</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>99921</t>
+          <t>100586</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,24%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>70,07%</t>
+          <t>70,54%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>161108</t>
+          <t>160463</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>192690</t>
+          <t>192228</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,79%</t>
+          <t>74,61%</t>
         </is>
       </c>
     </row>
@@ -5656,12 +5656,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>21099</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>40298</t>
+          <t>40780</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5671,12 +5671,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,08%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5691,12 +5691,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>67149</t>
+          <t>67403</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>100876</t>
+          <t>99768</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5706,12 +5706,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,76%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>41,55%</t>
+          <t>41,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5726,12 +5726,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>94920</t>
+          <t>95203</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133584</t>
+          <t>133687</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5741,12 +5741,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,81%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>32,03%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>134320</t>
+          <t>133838</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153519</t>
+          <t>153336</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>87,92%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>141905</t>
+          <t>143013</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>175632</t>
+          <t>175378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,24%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>283816</t>
+          <t>283713</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>322480</t>
+          <t>322197</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,97%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>77,26%</t>
+          <t>77,19%</t>
         </is>
       </c>
     </row>
@@ -5999,12 +5999,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>105641</t>
+          <t>105867</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>143942</t>
+          <t>143017</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>251097</t>
+          <t>248112</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>306449</t>
+          <t>305455</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6069,12 +6069,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>367801</t>
+          <t>364334</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>438824</t>
+          <t>433164</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6084,12 +6084,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,86%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,05%</t>
+          <t>31,63%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>447386</t>
+          <t>448311</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>485687</t>
+          <t>485461</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>75,66%</t>
+          <t>75,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>471482</t>
+          <t>472476</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>526834</t>
+          <t>529819</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>60,61%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,72%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>930435</t>
+          <t>936095</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1001458</t>
+          <t>1004925</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>68,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>73,14%</t>
+          <t>73,39%</t>
         </is>
       </c>
     </row>
@@ -6569,32 +6569,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>50528</t>
+          <t>53903</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>41749</t>
+          <t>44628</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>60580</t>
+          <t>63885</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>28,19%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>40,91%</t>
+          <t>39,12%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6604,32 +6604,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>83070</t>
+          <t>88367</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>74982</t>
+          <t>79747</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>90985</t>
+          <t>97506</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>42,02%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6639,32 +6639,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>133599</t>
+          <t>142270</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>121879</t>
+          <t>129146</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>146680</t>
+          <t>156118</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>37,36%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>44,96%</t>
+          <t>44,21%</t>
         </is>
       </c>
     </row>
@@ -6682,32 +6682,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>97555</t>
+          <t>109411</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>87503</t>
+          <t>99429</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>106334</t>
+          <t>118686</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>66,99%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>59,09%</t>
+          <t>60,88%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6717,32 +6717,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>95063</t>
+          <t>101436</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>87148</t>
+          <t>92297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>103151</t>
+          <t>110056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>53,37%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>57,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6752,32 +6752,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>192617</t>
+          <t>210847</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>179536</t>
+          <t>196999</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>204337</t>
+          <t>223971</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>55,04%</t>
+          <t>55,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>63,43%</t>
         </is>
       </c>
     </row>
@@ -6795,17 +6795,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6830,17 +6830,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>178133</t>
+          <t>189803</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6865,17 +6865,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>326216</t>
+          <t>353117</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6912,32 +6912,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41744</t>
+          <t>45138</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>34368</t>
+          <t>35784</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>51193</t>
+          <t>55189</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>30,97%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6947,32 +6947,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>90897</t>
+          <t>100236</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>80767</t>
+          <t>89206</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>101266</t>
+          <t>111916</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>41,79%</t>
+          <t>41,64%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>37,13%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,55%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -6982,32 +6982,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>132642</t>
+          <t>145374</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119042</t>
+          <t>131477</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>147180</t>
+          <t>161035</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>35,12%</t>
+          <t>34,7%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>31,52%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,44%</t>
         </is>
       </c>
     </row>
@@ -7025,32 +7025,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>118370</t>
+          <t>133066</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>108921</t>
+          <t>123015</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>125746</t>
+          <t>142420</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>69,03%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7060,32 +7060,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>126628</t>
+          <t>140491</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>116259</t>
+          <t>128811</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>136758</t>
+          <t>151521</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>58,21%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,45%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>62,87%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7095,32 +7095,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>244998</t>
+          <t>273556</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>230460</t>
+          <t>257895</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>258598</t>
+          <t>287453</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>64,88%</t>
+          <t>65,3%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>61,03%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>68,48%</t>
+          <t>68,62%</t>
         </is>
       </c>
     </row>
@@ -7138,17 +7138,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7173,17 +7173,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>217525</t>
+          <t>240727</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7208,17 +7208,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>377640</t>
+          <t>418930</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7255,32 +7255,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>27659</t>
+          <t>32238</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>20096</t>
+          <t>24019</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36544</t>
+          <t>43027</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,38%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7290,32 +7290,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61010</t>
+          <t>67756</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>16723</t>
+          <t>57546</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>149080</t>
+          <t>77911</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>38,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>32,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>41,43%</t>
+          <t>44,66%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7325,32 +7325,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>88668</t>
+          <t>99994</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>36968</t>
+          <t>85753</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>157919</t>
+          <t>114700</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>30,06%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>25,78%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>34,49%</t>
         </is>
       </c>
     </row>
@@ -7368,32 +7368,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>107800</t>
+          <t>125919</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>98915</t>
+          <t>115130</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>115363</t>
+          <t>134138</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>79,58%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>73,02%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>85,16%</t>
+          <t>84,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7403,32 +7403,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>298793</t>
+          <t>106685</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>210723</t>
+          <t>96530</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>343080</t>
+          <t>116895</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>61,16%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>55,34%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>67,01%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7438,32 +7438,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>406595</t>
+          <t>232604</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>337344</t>
+          <t>217898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>458295</t>
+          <t>246845</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>69,94%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>65,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>92,54%</t>
+          <t>74,22%</t>
         </is>
       </c>
     </row>
@@ -7481,17 +7481,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>135459</t>
+          <t>158157</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7516,17 +7516,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>359803</t>
+          <t>174441</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7551,17 +7551,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>495263</t>
+          <t>332598</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7598,32 +7598,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>43074</t>
+          <t>44178</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>34763</t>
+          <t>34988</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52202</t>
+          <t>53404</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>20,98%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>25,37%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7633,32 +7633,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>105910</t>
+          <t>114402</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>94249</t>
+          <t>102858</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>118477</t>
+          <t>127546</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>38,69%</t>
+          <t>39,01%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>34,43%</t>
+          <t>35,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,49%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7668,32 +7668,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>148984</t>
+          <t>158581</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>133344</t>
+          <t>141899</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>163935</t>
+          <t>174508</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,55%</t>
+          <t>34,64%</t>
         </is>
       </c>
     </row>
@@ -7711,32 +7711,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>157674</t>
+          <t>166354</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>148546</t>
+          <t>157128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>165985</t>
+          <t>175544</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>79,02%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>74,0%</t>
+          <t>74,63%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,68%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7746,32 +7746,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>167852</t>
+          <t>178845</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>155285</t>
+          <t>165701</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>179513</t>
+          <t>190389</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,31%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>65,57%</t>
+          <t>64,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7781,32 +7781,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>325526</t>
+          <t>345198</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>310575</t>
+          <t>329271</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>341166</t>
+          <t>361880</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>71,9%</t>
+          <t>71,83%</t>
         </is>
       </c>
     </row>
@@ -7824,17 +7824,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>200748</t>
+          <t>210532</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -7859,17 +7859,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>273762</t>
+          <t>293247</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -7894,17 +7894,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>474510</t>
+          <t>503779</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -7941,32 +7941,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>163005</t>
+          <t>175457</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>145589</t>
+          <t>158954</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>180902</t>
+          <t>197033</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>25,3%</t>
+          <t>24,71%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,38%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7976,32 +7976,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>340887</t>
+          <t>370762</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>179236</t>
+          <t>348962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>433745</t>
+          <t>390260</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>41,28%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>17,41%</t>
+          <t>38,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8011,32 +8011,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>503892</t>
+          <t>546218</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>344724</t>
+          <t>517575</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>586783</t>
+          <t>577032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>32,18%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>35,88%</t>
         </is>
       </c>
     </row>
@@ -8054,32 +8054,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>481399</t>
+          <t>534750</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>463502</t>
+          <t>513174</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>498815</t>
+          <t>551253</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>75,29%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,26%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,62%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8089,32 +8089,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>688337</t>
+          <t>527456</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>595479</t>
+          <t>507958</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>849988</t>
+          <t>549256</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>58,72%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>56,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>82,59%</t>
+          <t>61,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8124,32 +8124,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>1169736</t>
+          <t>1062206</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>1086845</t>
+          <t>1031392</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>1328904</t>
+          <t>1090849</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,4%</t>
+          <t>67,82%</t>
         </is>
       </c>
     </row>
@@ -8167,17 +8167,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>644404</t>
+          <t>710207</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8202,17 +8202,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>1029224</t>
+          <t>898218</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8237,17 +8237,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1673628</t>
+          <t>1608424</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
